--- a/docs/data/quests.xlsx
+++ b/docs/data/quests.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf67d8ea8c22b469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="2" r:id="Rafbda4150875452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="3" r:id="R9671e9be4ebe4bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Raf91756d4ae5418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="2" r:id="R720497cea8674736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="3" r:id="R5abcadb045ed432f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -601,7 +601,7 @@
         <x:v>DARK学项目练手</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>{"giverNpcId":"831434cb-2471-5f24-9fdf-0259fe149eae","completionGiverId":"d07dc3ae-a94f-5bf5-a352-b2c487682d31","requires":{"minAge":14,"expMax":5000},"cooldownSec":30,"rewardBase":25,"reward":{"experience":50,"potential":50,"money":40},"variants":[{"id":"91c4203d-9099-4316-b358-99100aaa14bc","title":"图书管理系统","hpCost":25,"rewardScale":1},{"id":"0dbe3d76-4635-4d2e-b5f1-cb4d595a8640","title":"CRM系统","hpCost":50,"rewardScale":1.5},{"id":"3f362f95-3dc5-4eb7-b672-b44c41246c7e","title":"ERP系统","hpCost":100,"rewardScale":2.4}],"lines":{"offer":"来得正好，我这里有个练手项目。","accepted":"我这有个【{target}】的活，你去干了吧。","inProgress":"安排给你的【{target}】咋还没做完呢，去隔壁电脑干活去。","tooExp":"你这身手，写这种新手项目屈才啦，去接点更大的活吧。","lowHp":"熬了大夜赶项目，你脸色发白，先歇口气，别硬撑。","done":"你在电脑前辛辛苦苦码完了【{target}】。{reward}","cooldown":"最近市场不景气，没活安排给你干。"}}</x:v>
+        <x:v>{"giverNpcId":"831434cb-2471-5f24-9fdf-0259fe149eae","completionGiverId":"d07dc3ae-a94f-5bf5-a352-b2c487682d31","requires":{"minAge":14,"expMax":5000},"cooldownSec":30,"rewardBase":25,"reward":{"experience":50,"potential":50,"money":40},"variants":[{"id":"91c4203d-9099-4316-b358-99100aaa14bc","title":"图书管理系统","hpCost":25},{"id":"0dbe3d76-4635-4d2e-b5f1-cb4d595a8640","title":"CRM系统","hpCost":50},{"id":"3f362f95-3dc5-4eb7-b672-b44c41246c7e","title":"ERP系统","hpCost":100}],"lines":{"offer":"来得正好，我这里有个练手项目。","accepted":"我这有个【{target}】的活，你去干了吧。","inProgress":"安排给你的【{target}】咋还没做完呢，去隔壁电脑干活去。","tooExp":"你这身手，写这种新手项目屈才啦，去接点更大的活吧。","lowHp":"熬了大夜赶项目，你脸色发白，先歇口气，别硬撑。","done":"你在电脑前辛辛苦苦码完了【{target}】。{reward}","cooldown":"最近市场不景气，没活安排给你干。"}}</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
